--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H448"/>
+  <dimension ref="A1:H452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14814,7 +14814,11 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr"/>
@@ -14836,7 +14840,11 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr"/>
@@ -14858,7 +14866,11 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr"/>
@@ -15084,6 +15096,94 @@
       <c r="G448" t="inlineStr"/>
       <c r="H448" t="inlineStr"/>
     </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0448-2026</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0449-2026</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0450-2026</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0451-2026</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -16472,10 +16472,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
-      <c r="G408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
       <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr"/>
       <c r="J408" t="inlineStr">
@@ -16493,8 +16509,16 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M408" t="inlineStr"/>
-      <c r="N408" t="inlineStr"/>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0407-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -17064,10 +17088,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
-      <c r="G424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr">
@@ -17077,8 +17117,16 @@
       </c>
       <c r="K424" t="inlineStr"/>
       <c r="L424" t="inlineStr"/>
-      <c r="M424" t="inlineStr"/>
-      <c r="N424" t="inlineStr"/>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0423-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -17096,10 +17144,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
-      <c r="G425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr">
@@ -17109,8 +17173,16 @@
       </c>
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr"/>
-      <c r="M425" t="inlineStr"/>
-      <c r="N425" t="inlineStr"/>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0424-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -17128,10 +17200,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
-      <c r="G426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr"/>
       <c r="J426" t="inlineStr">
@@ -17141,8 +17229,16 @@
       </c>
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr"/>
-      <c r="M426" t="inlineStr"/>
-      <c r="N426" t="inlineStr"/>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0425-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -17160,10 +17256,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
-      <c r="G427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr"/>
       <c r="J427" t="inlineStr">
@@ -17173,8 +17285,16 @@
       </c>
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr"/>
-      <c r="M427" t="inlineStr"/>
-      <c r="N427" t="inlineStr"/>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0426-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -17192,10 +17312,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr"/>
       <c r="J428" t="inlineStr">
@@ -17205,8 +17341,16 @@
       </c>
       <c r="K428" t="inlineStr"/>
       <c r="L428" t="inlineStr"/>
-      <c r="M428" t="inlineStr"/>
-      <c r="N428" t="inlineStr"/>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0427-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -17224,10 +17368,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
-      <c r="G429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr"/>
       <c r="J429" t="inlineStr">
@@ -17237,8 +17397,16 @@
       </c>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
-      <c r="M429" t="inlineStr"/>
-      <c r="N429" t="inlineStr"/>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0428-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -17256,10 +17424,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
-      <c r="G430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr"/>
       <c r="J430" t="inlineStr">
@@ -17269,8 +17453,16 @@
       </c>
       <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr"/>
-      <c r="M430" t="inlineStr"/>
-      <c r="N430" t="inlineStr"/>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0429-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -17288,10 +17480,26 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
-      <c r="G431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr"/>
       <c r="J431" t="inlineStr">
@@ -17301,8 +17509,16 @@
       </c>
       <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr"/>
-      <c r="M431" t="inlineStr"/>
-      <c r="N431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0430-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -17320,8 +17536,16 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
-      <c r="E432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr"/>
       <c r="H432" t="inlineStr"/>
@@ -17333,8 +17557,16 @@
       </c>
       <c r="K432" t="inlineStr"/>
       <c r="L432" t="inlineStr"/>
-      <c r="M432" t="inlineStr"/>
-      <c r="N432" t="inlineStr"/>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0431-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -17352,10 +17584,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
-      <c r="G433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr">
@@ -17365,8 +17613,16 @@
       </c>
       <c r="K433" t="inlineStr"/>
       <c r="L433" t="inlineStr"/>
-      <c r="M433" t="inlineStr"/>
-      <c r="N433" t="inlineStr"/>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0432-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -17384,10 +17640,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
-      <c r="G434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr"/>
       <c r="J434" t="inlineStr">
@@ -17397,8 +17669,16 @@
       </c>
       <c r="K434" t="inlineStr"/>
       <c r="L434" t="inlineStr"/>
-      <c r="M434" t="inlineStr"/>
-      <c r="N434" t="inlineStr"/>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0433-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -17416,10 +17696,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr"/>
       <c r="J435" t="inlineStr">
@@ -17429,8 +17725,16 @@
       </c>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
-      <c r="M435" t="inlineStr"/>
-      <c r="N435" t="inlineStr"/>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0434-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -17448,10 +17752,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
-      <c r="G436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr"/>
       <c r="J436" t="inlineStr">
@@ -17461,8 +17781,16 @@
       </c>
       <c r="K436" t="inlineStr"/>
       <c r="L436" t="inlineStr"/>
-      <c r="M436" t="inlineStr"/>
-      <c r="N436" t="inlineStr"/>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0435-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -17480,10 +17808,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
-      <c r="G437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr"/>
       <c r="J437" t="inlineStr">
@@ -17493,8 +17837,16 @@
       </c>
       <c r="K437" t="inlineStr"/>
       <c r="L437" t="inlineStr"/>
-      <c r="M437" t="inlineStr"/>
-      <c r="N437" t="inlineStr"/>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0436-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -17512,10 +17864,26 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
-      <c r="G438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr"/>
       <c r="J438" t="inlineStr">
@@ -17525,8 +17893,16 @@
       </c>
       <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr"/>
-      <c r="M438" t="inlineStr"/>
-      <c r="N438" t="inlineStr"/>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0437-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -17544,17 +17920,41 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
-      <c r="M439" t="inlineStr"/>
-      <c r="N439" t="inlineStr"/>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0438-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -17572,17 +17972,41 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
-      <c r="G440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
       <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
-      <c r="M440" t="inlineStr"/>
-      <c r="N440" t="inlineStr"/>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0439-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -17600,17 +18024,41 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
       <c r="J441" t="inlineStr"/>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
-      <c r="M441" t="inlineStr"/>
-      <c r="N441" t="inlineStr"/>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0440-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -17628,17 +18076,41 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
-      <c r="M442" t="inlineStr"/>
-      <c r="N442" t="inlineStr"/>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0441-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -17656,17 +18128,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
-      <c r="G443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
-      <c r="M443" t="inlineStr"/>
-      <c r="N443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0442-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -17684,17 +18180,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
-      <c r="G444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr"/>
-      <c r="M444" t="inlineStr"/>
-      <c r="N444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0443-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -17712,17 +18232,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
-      <c r="G445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr"/>
       <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr"/>
-      <c r="M445" t="inlineStr"/>
-      <c r="N445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0444-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -17740,17 +18284,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
-      <c r="G446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
       <c r="J446" t="inlineStr"/>
       <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr"/>
-      <c r="M446" t="inlineStr"/>
-      <c r="N446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0445-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -17768,17 +18336,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
-      <c r="G447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr"/>
-      <c r="M447" t="inlineStr"/>
-      <c r="N447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0446-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -17796,17 +18388,41 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
-      <c r="G448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
       <c r="J448" t="inlineStr"/>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
-      <c r="M448" t="inlineStr"/>
-      <c r="N448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0447-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -17824,17 +18440,41 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
-      <c r="G449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
-      <c r="M449" t="inlineStr"/>
-      <c r="N449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0448-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -17852,17 +18492,49 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
-      <c r="I450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr"/>
-      <c r="M450" t="inlineStr"/>
-      <c r="N450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0449-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -17880,17 +18552,41 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
-      <c r="G451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
-      <c r="M451" t="inlineStr"/>
-      <c r="N451" t="inlineStr"/>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0450-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -17908,17 +18604,41 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
-      <c r="G452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
       <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr"/>
-      <c r="M452" t="inlineStr"/>
-      <c r="N452" t="inlineStr"/>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>objeto de esta licitación.</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0451-2026.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,72 +429,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No. Licitación</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Convocatoria</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Publicada</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Junta (prog.)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Apertura (prog.)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fallo (prog.)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Acta Junta</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Acta Apertura</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Acta Fallo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Objeto</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -18512,16 +18524,8 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
       <c r="J450" t="inlineStr"/>
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr"/>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N452"/>
+  <dimension ref="A1:O452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,11 @@
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Solicitante</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -539,6 +544,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +585,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -615,6 +622,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -655,6 +663,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -695,6 +704,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -735,6 +745,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -775,6 +786,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -815,6 +827,7 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -855,6 +868,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -895,6 +909,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -935,6 +950,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -975,6 +991,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1015,6 +1032,7 @@
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1055,6 +1073,7 @@
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1095,6 +1114,7 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1135,6 +1155,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1175,6 +1196,7 @@
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1215,6 +1237,7 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1255,6 +1278,7 @@
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1295,6 +1319,7 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1335,6 +1360,7 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1371,6 +1397,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1411,6 +1438,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1451,6 +1479,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1491,6 +1520,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1531,6 +1561,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1571,6 +1602,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1611,6 +1643,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1651,6 +1684,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1691,6 +1725,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1731,6 +1766,7 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1771,6 +1807,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1811,6 +1848,7 @@
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1847,6 +1885,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1887,6 +1926,7 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1927,6 +1967,7 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1967,6 +2008,7 @@
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2003,6 +2045,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2043,6 +2086,7 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2083,6 +2127,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2123,6 +2168,7 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2163,6 +2209,7 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2199,6 +2246,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2239,6 +2287,7 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2279,6 +2328,7 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2319,6 +2369,7 @@
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2359,6 +2410,7 @@
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2399,6 +2451,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2439,6 +2492,7 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2479,6 +2533,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2519,6 +2574,7 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2559,6 +2615,7 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2599,6 +2656,7 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2635,6 +2693,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2675,6 +2734,7 @@
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2715,6 +2775,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2755,6 +2816,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2795,6 +2857,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2835,6 +2898,7 @@
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2875,6 +2939,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2915,6 +2980,7 @@
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2951,6 +3017,7 @@
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2991,6 +3058,7 @@
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3031,6 +3099,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3071,6 +3140,7 @@
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3111,6 +3181,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3151,6 +3222,7 @@
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3191,6 +3263,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3231,6 +3304,7 @@
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3267,6 +3341,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3307,6 +3382,7 @@
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3347,6 +3423,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3387,6 +3464,7 @@
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3427,6 +3505,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3467,6 +3546,7 @@
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3507,6 +3587,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3547,6 +3628,7 @@
       </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3587,6 +3669,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3627,6 +3710,7 @@
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3663,6 +3747,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3703,6 +3788,7 @@
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3743,6 +3829,7 @@
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3779,6 +3866,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3815,6 +3903,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3855,6 +3944,7 @@
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3891,6 +3981,7 @@
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3931,6 +4022,7 @@
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3971,6 +4063,7 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4011,6 +4104,7 @@
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4051,6 +4145,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4091,6 +4186,7 @@
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4131,6 +4227,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4171,6 +4268,7 @@
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4211,6 +4309,7 @@
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4251,6 +4350,7 @@
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4291,6 +4391,7 @@
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4331,6 +4432,7 @@
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4371,6 +4473,7 @@
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4411,6 +4514,7 @@
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4451,6 +4555,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4491,6 +4596,7 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4531,6 +4637,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4571,6 +4678,7 @@
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4611,6 +4719,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4651,6 +4760,7 @@
       </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4691,6 +4801,7 @@
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4731,6 +4842,7 @@
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4771,6 +4883,7 @@
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4807,6 +4920,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4847,6 +4961,7 @@
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4887,6 +5002,7 @@
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4927,6 +5043,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4967,6 +5084,7 @@
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5007,6 +5125,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5047,6 +5166,7 @@
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5083,6 +5203,7 @@
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5123,6 +5244,7 @@
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5163,6 +5285,7 @@
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5203,6 +5326,7 @@
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5243,6 +5367,7 @@
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5283,6 +5408,7 @@
       </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5323,6 +5449,7 @@
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5363,6 +5490,7 @@
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5403,6 +5531,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5443,6 +5572,7 @@
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5483,6 +5613,7 @@
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5523,6 +5654,7 @@
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5563,6 +5695,7 @@
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5599,6 +5732,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5635,6 +5769,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5675,6 +5810,7 @@
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5715,6 +5851,7 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5755,6 +5892,7 @@
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5795,6 +5933,7 @@
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5831,6 +5970,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5871,6 +6011,7 @@
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5911,6 +6052,7 @@
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5947,6 +6089,7 @@
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5987,6 +6130,7 @@
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6027,6 +6171,7 @@
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6067,6 +6212,7 @@
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6107,6 +6253,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6143,6 +6290,7 @@
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6183,6 +6331,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6223,6 +6372,7 @@
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6259,6 +6409,7 @@
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6299,6 +6450,7 @@
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6339,6 +6491,7 @@
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6375,6 +6528,7 @@
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6415,6 +6569,7 @@
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6455,6 +6610,7 @@
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6495,6 +6651,7 @@
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6535,6 +6692,7 @@
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6575,6 +6733,7 @@
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6615,6 +6774,7 @@
       </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6655,6 +6815,7 @@
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6695,6 +6856,7 @@
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6735,6 +6897,7 @@
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6775,6 +6938,7 @@
       </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6811,6 +6975,7 @@
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6851,6 +7016,7 @@
       </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6891,6 +7057,7 @@
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6927,6 +7094,7 @@
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6967,6 +7135,7 @@
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7003,6 +7172,7 @@
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7043,6 +7213,7 @@
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7083,6 +7254,7 @@
       </c>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7123,6 +7295,7 @@
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7163,6 +7336,7 @@
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7203,6 +7377,7 @@
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7243,6 +7418,7 @@
       </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7283,6 +7459,7 @@
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7323,6 +7500,7 @@
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7363,6 +7541,7 @@
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7403,6 +7582,7 @@
       </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7443,6 +7623,7 @@
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7479,6 +7660,7 @@
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7519,6 +7701,7 @@
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7559,6 +7742,7 @@
       </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7599,6 +7783,7 @@
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7639,6 +7824,7 @@
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7675,6 +7861,7 @@
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7715,6 +7902,7 @@
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7755,6 +7943,7 @@
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7795,6 +7984,7 @@
       </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7835,6 +8025,7 @@
       </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7875,6 +8066,7 @@
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7915,6 +8107,7 @@
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7955,6 +8148,7 @@
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7995,6 +8189,7 @@
       </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8035,6 +8230,7 @@
       </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8075,6 +8271,7 @@
       </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8115,6 +8312,7 @@
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8151,6 +8349,7 @@
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8191,6 +8390,7 @@
       </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8231,6 +8431,7 @@
       </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8271,6 +8472,7 @@
       </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8307,6 +8509,7 @@
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8347,6 +8550,7 @@
       </c>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8387,6 +8591,7 @@
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8427,6 +8632,7 @@
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8467,6 +8673,7 @@
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8507,6 +8714,7 @@
       </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8547,6 +8755,7 @@
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8587,6 +8796,7 @@
       </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8627,6 +8837,7 @@
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8667,6 +8878,7 @@
       </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8707,6 +8919,7 @@
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8747,6 +8960,7 @@
       </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8787,6 +9001,7 @@
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8827,6 +9042,7 @@
       </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8867,6 +9083,7 @@
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8907,6 +9124,7 @@
       </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8947,6 +9165,7 @@
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8987,6 +9206,7 @@
       </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9027,6 +9247,7 @@
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9067,6 +9288,7 @@
       </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9107,6 +9329,7 @@
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9147,6 +9370,7 @@
       </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9187,6 +9411,7 @@
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9227,6 +9452,7 @@
       </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9263,6 +9489,7 @@
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9303,6 +9530,7 @@
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9343,6 +9571,7 @@
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9383,6 +9612,7 @@
       </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9423,6 +9653,7 @@
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9463,6 +9694,7 @@
       </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9503,6 +9735,7 @@
       </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9539,6 +9772,7 @@
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9579,6 +9813,7 @@
       </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9619,6 +9854,7 @@
       </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9659,6 +9895,7 @@
       </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9699,6 +9936,7 @@
       </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9739,6 +9977,7 @@
       </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9779,6 +10018,7 @@
       </c>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9815,6 +10055,7 @@
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9855,6 +10096,7 @@
       </c>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9895,6 +10137,7 @@
       </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9935,6 +10178,7 @@
       </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -9975,6 +10219,7 @@
       </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10015,6 +10260,7 @@
       </c>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10055,6 +10301,7 @@
       </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10095,6 +10342,7 @@
       </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10135,6 +10383,7 @@
       </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10175,6 +10424,7 @@
       </c>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10215,6 +10465,7 @@
       </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10255,6 +10506,7 @@
       </c>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10295,6 +10547,7 @@
       </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10335,6 +10588,7 @@
       </c>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10375,6 +10629,7 @@
       </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10415,6 +10670,7 @@
       </c>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10455,6 +10711,7 @@
       </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10495,6 +10752,7 @@
       </c>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10535,6 +10793,7 @@
       </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10575,6 +10834,7 @@
       </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10611,6 +10871,7 @@
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10651,6 +10912,7 @@
       </c>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10691,6 +10953,7 @@
       </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10731,6 +10994,7 @@
       </c>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10771,6 +11035,7 @@
       </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10811,6 +11076,7 @@
       </c>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10847,6 +11113,7 @@
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -10887,6 +11154,7 @@
       </c>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -10927,6 +11195,7 @@
       </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10967,6 +11236,7 @@
       </c>
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11007,6 +11277,7 @@
       </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11047,6 +11318,7 @@
       </c>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11087,6 +11359,7 @@
       </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11127,6 +11400,7 @@
       </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11167,6 +11441,7 @@
       </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11203,6 +11478,7 @@
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11243,6 +11519,7 @@
       </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11279,6 +11556,7 @@
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11319,6 +11597,7 @@
       </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11359,6 +11638,7 @@
       </c>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11399,6 +11679,7 @@
       </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11439,6 +11720,7 @@
       </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11479,6 +11761,7 @@
       </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11515,6 +11798,7 @@
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11555,6 +11839,7 @@
       </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11595,6 +11880,7 @@
       </c>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11635,6 +11921,7 @@
       </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11675,6 +11962,7 @@
       </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11707,6 +11995,7 @@
       <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11747,6 +12036,7 @@
       </c>
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11783,6 +12073,7 @@
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11823,6 +12114,7 @@
       </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -11863,6 +12155,7 @@
       </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11903,6 +12196,7 @@
       </c>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11943,6 +12237,7 @@
       </c>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11979,6 +12274,7 @@
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12019,6 +12315,7 @@
       </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12059,6 +12356,7 @@
       </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12099,6 +12397,7 @@
       </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12139,6 +12438,7 @@
       </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12175,6 +12475,7 @@
       <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12211,6 +12512,7 @@
       <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12247,6 +12549,7 @@
       <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12287,6 +12590,7 @@
       </c>
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -12327,6 +12631,7 @@
       </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12367,6 +12672,7 @@
       </c>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12403,6 +12709,7 @@
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12443,6 +12750,7 @@
       </c>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12483,6 +12791,7 @@
       </c>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12519,6 +12828,7 @@
       <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12559,6 +12869,7 @@
       </c>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12595,6 +12906,7 @@
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12635,6 +12947,7 @@
       </c>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12671,6 +12984,7 @@
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -12711,6 +13025,7 @@
       </c>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12751,6 +13066,7 @@
       </c>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -12791,6 +13107,7 @@
       </c>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12831,6 +13148,7 @@
       </c>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -12871,6 +13189,7 @@
       </c>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12911,6 +13230,7 @@
       </c>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -12951,6 +13271,7 @@
       </c>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -12991,6 +13312,7 @@
       </c>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13031,6 +13353,7 @@
       </c>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13067,6 +13390,7 @@
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13107,6 +13431,7 @@
       </c>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13147,6 +13472,7 @@
       </c>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13183,6 +13509,7 @@
       <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13223,6 +13550,7 @@
       </c>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13263,6 +13591,7 @@
       </c>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13303,6 +13632,7 @@
       </c>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13343,6 +13673,7 @@
       </c>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13383,6 +13714,7 @@
       </c>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13419,6 +13751,7 @@
       <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13459,6 +13792,7 @@
       </c>
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13499,6 +13833,7 @@
       </c>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13539,6 +13874,7 @@
       </c>
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -13579,6 +13915,7 @@
       </c>
       <c r="M333" t="inlineStr"/>
       <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13619,6 +13956,7 @@
       </c>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13659,6 +13997,7 @@
       </c>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13699,6 +14038,7 @@
       </c>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -13735,6 +14075,7 @@
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13775,6 +14116,7 @@
       </c>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -13815,6 +14157,7 @@
       </c>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -13851,6 +14194,7 @@
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13891,6 +14235,7 @@
       </c>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -13931,6 +14276,7 @@
       </c>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -13971,6 +14317,7 @@
       </c>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14011,6 +14358,7 @@
       </c>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14047,6 +14395,7 @@
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14087,6 +14436,7 @@
       </c>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14127,6 +14477,7 @@
       </c>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14167,6 +14518,7 @@
       </c>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14203,6 +14555,7 @@
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14243,6 +14596,7 @@
       </c>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14283,6 +14637,7 @@
       </c>
       <c r="M351" t="inlineStr"/>
       <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14323,6 +14678,7 @@
       </c>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14363,6 +14719,7 @@
       </c>
       <c r="M353" t="inlineStr"/>
       <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -14403,6 +14760,7 @@
       </c>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14443,6 +14801,7 @@
       </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14483,6 +14842,7 @@
       </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14523,6 +14883,7 @@
       </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14559,6 +14920,7 @@
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="inlineStr"/>
       <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14599,6 +14961,7 @@
       </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14639,6 +15002,7 @@
       </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14679,6 +15043,7 @@
       </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14719,6 +15084,7 @@
       </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14759,6 +15125,7 @@
       </c>
       <c r="M363" t="inlineStr"/>
       <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -14795,6 +15162,7 @@
       <c r="L364" t="inlineStr"/>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -14831,6 +15199,7 @@
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr"/>
       <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14871,6 +15240,7 @@
       </c>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -14911,6 +15281,7 @@
       </c>
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -14947,6 +15318,7 @@
       <c r="L368" t="inlineStr"/>
       <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -14987,6 +15359,7 @@
       </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15027,6 +15400,7 @@
       </c>
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15067,6 +15441,7 @@
       </c>
       <c r="M371" t="inlineStr"/>
       <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15107,6 +15482,7 @@
       </c>
       <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -15143,6 +15519,7 @@
       <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15183,6 +15560,7 @@
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15223,6 +15601,7 @@
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -15263,6 +15642,7 @@
       </c>
       <c r="M376" t="inlineStr"/>
       <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -15303,6 +15683,7 @@
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr"/>
+      <c r="O377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -15343,6 +15724,7 @@
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr"/>
+      <c r="O378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -15379,6 +15761,7 @@
       <c r="L379" t="inlineStr"/>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -15415,6 +15798,7 @@
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -15451,6 +15835,7 @@
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -15487,6 +15872,7 @@
       <c r="L382" t="inlineStr"/>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -15527,6 +15913,7 @@
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -15567,6 +15954,7 @@
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -15607,6 +15995,7 @@
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -15647,6 +16036,7 @@
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -15687,6 +16077,7 @@
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15727,6 +16118,7 @@
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -15767,6 +16159,7 @@
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -15807,6 +16200,7 @@
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -15839,6 +16233,7 @@
       <c r="L391" t="inlineStr"/>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -15879,6 +16274,7 @@
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -15919,6 +16315,7 @@
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -15959,6 +16356,7 @@
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -15999,6 +16397,7 @@
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16039,6 +16438,7 @@
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16079,6 +16479,7 @@
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16115,6 +16516,7 @@
       <c r="L398" t="inlineStr"/>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -16155,6 +16557,7 @@
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -16195,6 +16598,7 @@
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -16235,6 +16639,7 @@
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -16275,6 +16680,7 @@
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -16315,6 +16721,7 @@
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -16351,6 +16758,7 @@
       <c r="L404" t="inlineStr"/>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -16391,6 +16799,7 @@
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -16431,6 +16840,7 @@
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -16467,6 +16877,7 @@
       <c r="L407" t="inlineStr"/>
       <c r="M407" t="inlineStr"/>
       <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -16523,10 +16934,15 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Vehículos y Equipo Terrestre</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0407-2026.pdf</t>
         </is>
@@ -16567,6 +16983,7 @@
       <c r="L409" t="inlineStr"/>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -16607,6 +17024,7 @@
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -16647,6 +17065,7 @@
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -16683,6 +17102,7 @@
       <c r="L412" t="inlineStr"/>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -16723,6 +17143,7 @@
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -16763,6 +17184,7 @@
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -16803,6 +17225,7 @@
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -16839,6 +17262,7 @@
       <c r="L416" t="inlineStr"/>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -16875,6 +17299,7 @@
       <c r="L417" t="inlineStr"/>
       <c r="M417" t="inlineStr"/>
       <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -16911,6 +17336,7 @@
       <c r="L418" t="inlineStr"/>
       <c r="M418" t="inlineStr"/>
       <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -16947,6 +17373,7 @@
       <c r="L419" t="inlineStr"/>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -16987,6 +17414,7 @@
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17019,6 +17447,7 @@
       <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr"/>
+      <c r="O421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17051,6 +17480,7 @@
       <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17083,6 +17513,7 @@
       <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -17131,10 +17562,15 @@
       <c r="L424" t="inlineStr"/>
       <c r="M424" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Activos Intangibles (Sistema Integral de Enseñanza, aprendizaje y certificación del idioma inglés)</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
+        <is>
+          <t>el Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0423-2026.pdf</t>
         </is>
@@ -17187,10 +17623,15 @@
       <c r="L425" t="inlineStr"/>
       <c r="M425" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Vestuario y Uniformes</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Operación Policial de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0424-2026.pdf</t>
         </is>
@@ -17243,10 +17684,15 @@
       <c r="L426" t="inlineStr"/>
       <c r="M426" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0425-2026.pdf</t>
         </is>
@@ -17299,10 +17745,15 @@
       <c r="L427" t="inlineStr"/>
       <c r="M427" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Material de Oficina, Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Material de Limpieza</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0426-2026.pdf</t>
         </is>
@@ -17355,10 +17806,15 @@
       <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Combustibles y Lubricantes para Vehículos y Equipos Terrestres, Refacciones para Vehículos y Equipos de Transporte</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0427-2026.pdf</t>
         </is>
@@ -17411,10 +17867,15 @@
       <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Prendas de Seguridad y Protección Personal, Identificadores e Iconos de Señalización, Herramientas Menores</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0428-2026.pdf</t>
         </is>
@@ -17467,10 +17928,15 @@
       <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Arrendamiento de Maquinaria, Otros Equipos y Herramientas</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0429-2026.pdf</t>
         </is>
@@ -17523,10 +17989,15 @@
       <c r="L431" t="inlineStr"/>
       <c r="M431" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Prendas de Seguridad y Protección Personal</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0430-2026.pdf</t>
         </is>
@@ -17571,10 +18042,15 @@
       <c r="L432" t="inlineStr"/>
       <c r="M432" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Uniformes Escolares</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo, el Colegio de Bachilleres del Estado de Hidalgo, el Bachillerato del Estado de Hidalgo y el Colegio de Estudios Científicos y Tecnológicos del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0431-2026.pdf</t>
         </is>
@@ -17627,10 +18103,15 @@
       <c r="L433" t="inlineStr"/>
       <c r="M433" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Asignación de Combustible a través de Monederos Electrónicos</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0432-2026.pdf</t>
         </is>
@@ -17683,10 +18164,15 @@
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0433-2026.pdf</t>
         </is>
@@ -17739,10 +18225,15 @@
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Material Eléctrico, Artículos Metálicos para la Construcción</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0434-2026.pdf</t>
         </is>
@@ -17795,10 +18286,15 @@
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Artículos Metálicos para la Construcción, Otros Materiales y Artículos de Construcción y Reparación, Identificadores e Iconos De Señalización</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0435-2026.pdf</t>
         </is>
@@ -17851,10 +18347,15 @@
       <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Materiales para el Mantenimiento de Señalizaciones</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0436-2026.pdf</t>
         </is>
@@ -17907,10 +18408,15 @@
       <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
+        <is>
+          <t>los Centros de Rehabilitación Integral Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0437-2026.pdf</t>
         </is>
@@ -17959,10 +18465,15 @@
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicios Integrales</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
+        <is>
+          <t>la Dirección General de Formación y Competitividad Turística de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0438-2026.pdf</t>
         </is>
@@ -18011,10 +18522,15 @@
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicios de Acceso de Internet, Redes y Procesamiento de Información</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0439-2026.pdf</t>
         </is>
@@ -18063,10 +18579,15 @@
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
+        <is>
+          <t>la Subsecretaria del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación, e Inteligencia de la Secretaría de Seguridad Pública del Poder Ejecutivo del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0440-2026.pdf</t>
         </is>
@@ -18115,10 +18636,15 @@
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Inclusión y Desarrollo y la Subsecretaría de Participación Social y Fomento Artesanal de la Secretaría de Bienestar e Inclusión Social del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0441-2026.pdf</t>
         </is>
@@ -18167,10 +18693,15 @@
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Mantenimiento de Maquinaria y Equipo (Segundo Procedimiento)</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
+        <is>
+          <t>la Dirección General de Cuencas y Planeación Hídrica, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0442-2026.pdf</t>
         </is>
@@ -18219,10 +18750,15 @@
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Sustancias Químicas</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
+        <is>
+          <t>la Dirección General de Gestión de Calidad del Aire, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0443-2026.pdf</t>
         </is>
@@ -18271,10 +18807,15 @@
       <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicio de Fumigación</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0444-2026.pdf</t>
         </is>
@@ -18323,10 +18864,15 @@
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Materiales, Accesorios y Suministros de Laboratorio, Refacciones y Accesorios Menores de Equipo e Instrumental Médico y de Laboratorio</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
+        <is>
+          <t>la Dirección General de Gestión de Calidad del Aire, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0445-2026.pdf</t>
         </is>
@@ -18375,10 +18921,15 @@
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicio de Fumigación</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
+        <is>
+          <t>la Secretaría del Trabajo y Previsión Social, Secretaría de Contraloría, Secretaría de Educación Pública, Secretaría de Seguridad Pública, Secretaría de Turismo, Secretaría de Desarrollo Económico, Secretaría de Medio Ambiente y Recursos Naturales, Secretaría de Agricultura y Desarrollo Rural, Unida</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0446-2026.pdf</t>
         </is>
@@ -18427,10 +18978,15 @@
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicios Integrales (Segundo Procedimiento)</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0447-2026.pdf</t>
         </is>
@@ -18479,10 +19035,15 @@
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Otros Arrendamientos para el evento “Viviendo en Plenitud”</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
+        <is>
+          <t>la Dirección de Asistencia Social del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0448-2026.pdf</t>
         </is>
@@ -18531,10 +19092,15 @@
       <c r="L450" t="inlineStr"/>
       <c r="M450" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Servicio de Alimentos y Servicio de Impresiones para el evento “Viviendo en Plenitud”</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
+        <is>
+          <t>la Dirección de Asistencia Social del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0449-2026.pdf</t>
         </is>
@@ -18583,10 +19149,15 @@
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Equipo Médico y de Laboratorio (Electromiógrafo)</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0450-2026.pdf</t>
         </is>
@@ -18635,10 +19206,15 @@
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
-          <t>objeto de esta licitación.</t>
+          <t>Instrumental Médico y de Laboratorio</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0451-2026.pdf</t>
         </is>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,77 +417,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>No. Licitación</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Convocatoria</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Publicada</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Junta (prog.)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Apertura (prog.)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Fallo (prog.)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Acta Junta</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Acta Apertura</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Acta Fallo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Objeto</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Solicitante</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -16292,10 +16280,26 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
-      <c r="G393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
       <c r="J393" t="inlineStr">
@@ -16313,9 +16317,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr"/>
-      <c r="N393" t="inlineStr"/>
-      <c r="O393" t="inlineStr"/>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>Servicio global para realización de evento del Día del bombero (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo en conjunto con la Secretaría de Seguridad Pública del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0392-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -16333,10 +16349,26 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
-      <c r="G394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
       <c r="J394" t="inlineStr">
@@ -16354,9 +16386,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M394" t="inlineStr"/>
-      <c r="N394" t="inlineStr"/>
-      <c r="O394" t="inlineStr"/>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>Servicio global para realización de evento del Día del Policía (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo en conjunto con la Secretaría de Seguridad Pública del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0393-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -16374,10 +16418,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
-      <c r="G395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
       <c r="J395" t="inlineStr">
@@ -16395,9 +16455,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M395" t="inlineStr"/>
-      <c r="N395" t="inlineStr"/>
-      <c r="O395" t="inlineStr"/>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Maquinaria y Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0394-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16415,10 +16487,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
       <c r="J396" t="inlineStr">
@@ -16436,9 +16524,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
-      <c r="O396" t="inlineStr"/>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0395-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16456,10 +16556,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
       <c r="J397" t="inlineStr">
@@ -16477,9 +16593,21 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
-      <c r="O397" t="inlineStr"/>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0396-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16497,10 +16625,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
-      <c r="G398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
       <c r="J398" t="inlineStr">
@@ -16514,9 +16658,21 @@
         </is>
       </c>
       <c r="L398" t="inlineStr"/>
-      <c r="M398" t="inlineStr"/>
-      <c r="N398" t="inlineStr"/>
-      <c r="O398" t="inlineStr"/>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>la Dirección General de Gestión de Calidad del Aire, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0397-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -16534,10 +16690,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
-      <c r="G399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
       <c r="J399" t="inlineStr">
@@ -16555,9 +16727,21 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="M399" t="inlineStr"/>
-      <c r="N399" t="inlineStr"/>
-      <c r="O399" t="inlineStr"/>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>la Dirección General de Cuencas y Planeación Hídrica, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0398-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -16575,10 +16759,26 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
-      <c r="G400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr"/>
       <c r="J400" t="inlineStr">
@@ -16596,9 +16796,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M400" t="inlineStr"/>
-      <c r="N400" t="inlineStr"/>
-      <c r="O400" t="inlineStr"/>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>Productos Alimenticios</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0399-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -16616,10 +16828,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
-      <c r="G401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr"/>
       <c r="J401" t="inlineStr">
@@ -16637,9 +16865,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M401" t="inlineStr"/>
-      <c r="N401" t="inlineStr"/>
-      <c r="O401" t="inlineStr"/>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>Equipo Médico y de Laboratorio (Electromiógrafo)</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0400-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -16657,10 +16897,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
-      <c r="G402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr"/>
       <c r="J402" t="inlineStr">
@@ -16678,9 +16934,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M402" t="inlineStr"/>
-      <c r="N402" t="inlineStr"/>
-      <c r="O402" t="inlineStr"/>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>la Junta General de Asistencia del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0401-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -16698,10 +16966,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
-      <c r="G403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr"/>
       <c r="J403" t="inlineStr">
@@ -16719,9 +17003,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
-      <c r="O403" t="inlineStr"/>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>Medicinas y Productos Farmacéuticos</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0402-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -16739,10 +17035,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
-      <c r="G404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr"/>
       <c r="J404" t="inlineStr">
@@ -16756,9 +17068,21 @@
         </is>
       </c>
       <c r="L404" t="inlineStr"/>
-      <c r="M404" t="inlineStr"/>
-      <c r="N404" t="inlineStr"/>
-      <c r="O404" t="inlineStr"/>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0403-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -16776,10 +17100,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
-      <c r="G405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr"/>
       <c r="J405" t="inlineStr">
@@ -16797,9 +17137,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M405" t="inlineStr"/>
-      <c r="N405" t="inlineStr"/>
-      <c r="O405" t="inlineStr"/>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>Ayudas Sociales a Personas</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>la Dirección de Alimentación y Desarrollo Comunitario del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo, en coordinación con el Almacén General de Pachuca</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0404-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -16817,10 +17169,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr">
@@ -16838,9 +17206,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M406" t="inlineStr"/>
-      <c r="N406" t="inlineStr"/>
-      <c r="O406" t="inlineStr"/>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>Equipo Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>el Centro de Rehabilitación Integral Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0405-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -16858,10 +17238,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
-      <c r="G407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr"/>
       <c r="J407" t="inlineStr">
@@ -16875,9 +17271,21 @@
         </is>
       </c>
       <c r="L407" t="inlineStr"/>
-      <c r="M407" t="inlineStr"/>
-      <c r="N407" t="inlineStr"/>
-      <c r="O407" t="inlineStr"/>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0406-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -16964,10 +17372,26 @@
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr"/>
       <c r="J409" t="inlineStr">
@@ -16981,9 +17405,21 @@
         </is>
       </c>
       <c r="L409" t="inlineStr"/>
-      <c r="M409" t="inlineStr"/>
-      <c r="N409" t="inlineStr"/>
-      <c r="O409" t="inlineStr"/>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>Servicio Global ("Día Internacional de los Pueblos Indígenas")</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0408-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -17001,10 +17437,26 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr"/>
       <c r="J410" t="inlineStr">
@@ -17022,9 +17474,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M410" t="inlineStr"/>
-      <c r="N410" t="inlineStr"/>
-      <c r="O410" t="inlineStr"/>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>Asignación de apoyos económicos a través de monederos electrónicos</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0409-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -17042,10 +17506,26 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr"/>
       <c r="J411" t="inlineStr">
@@ -17063,9 +17543,21 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M411" t="inlineStr"/>
-      <c r="N411" t="inlineStr"/>
-      <c r="O411" t="inlineStr"/>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>Asignación de apoyos económicos a través de monederos electrónicos</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0410-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -17083,10 +17575,26 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr"/>
       <c r="J412" t="inlineStr">
@@ -17100,9 +17608,21 @@
         </is>
       </c>
       <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" t="inlineStr"/>
-      <c r="O412" t="inlineStr"/>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>Mobiliario para los Laboratorios STEM</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0411-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -17120,10 +17640,26 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr"/>
       <c r="J413" t="inlineStr">
@@ -17141,9 +17677,21 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M413" t="inlineStr"/>
-      <c r="N413" t="inlineStr"/>
-      <c r="O413" t="inlineStr"/>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>Prendas de Seguridad y Protección Personal</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0412-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -17161,10 +17709,26 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr"/>
       <c r="J414" t="inlineStr">
@@ -17182,9 +17746,21 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M414" t="inlineStr"/>
-      <c r="N414" t="inlineStr"/>
-      <c r="O414" t="inlineStr"/>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0413-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -17202,10 +17778,26 @@
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr"/>
       <c r="J415" t="inlineStr">
@@ -17223,9 +17815,21 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" t="inlineStr"/>
-      <c r="O415" t="inlineStr"/>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>Artículos Metálicos para la Construcción</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0414-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -17243,10 +17847,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr"/>
       <c r="J416" t="inlineStr">
@@ -17260,9 +17880,21 @@
         </is>
       </c>
       <c r="L416" t="inlineStr"/>
-      <c r="M416" t="inlineStr"/>
-      <c r="N416" t="inlineStr"/>
-      <c r="O416" t="inlineStr"/>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>Libros de Texto</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>el Colegio de Bachilleres del Estado de Hidalgo, el Colegio de Estudios Científicos y Tecnológicos del Estado de Hidalgo, el Colegio de Educación Profesional Técnica del Estado de Hidalgo y por el Bachillerato del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0415-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17280,10 +17912,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr"/>
       <c r="J417" t="inlineStr">
@@ -17297,9 +17945,21 @@
         </is>
       </c>
       <c r="L417" t="inlineStr"/>
-      <c r="M417" t="inlineStr"/>
-      <c r="N417" t="inlineStr"/>
-      <c r="O417" t="inlineStr"/>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Vehículos</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0416-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17317,10 +17977,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr">
@@ -17334,9 +18010,21 @@
         </is>
       </c>
       <c r="L418" t="inlineStr"/>
-      <c r="M418" t="inlineStr"/>
-      <c r="N418" t="inlineStr"/>
-      <c r="O418" t="inlineStr"/>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0417-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -17354,10 +18042,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
-      <c r="G419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr">
@@ -17371,9 +18075,21 @@
         </is>
       </c>
       <c r="L419" t="inlineStr"/>
-      <c r="M419" t="inlineStr"/>
-      <c r="N419" t="inlineStr"/>
-      <c r="O419" t="inlineStr"/>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>Muebles, Excepto De Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0418-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -17391,10 +18107,26 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
-      <c r="G420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr">
@@ -17412,9 +18144,21 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr"/>
-      <c r="N420" t="inlineStr"/>
-      <c r="O420" t="inlineStr"/>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>Servicio global para realización de eventos</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0419-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17432,10 +18176,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
-      <c r="G421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr">
@@ -17445,9 +18205,21 @@
       </c>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
-      <c r="M421" t="inlineStr"/>
-      <c r="N421" t="inlineStr"/>
-      <c r="O421" t="inlineStr"/>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>Servicios de Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0420-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17465,10 +18237,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
-      <c r="G422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr"/>
       <c r="J422" t="inlineStr">
@@ -17478,9 +18266,21 @@
       </c>
       <c r="K422" t="inlineStr"/>
       <c r="L422" t="inlineStr"/>
-      <c r="M422" t="inlineStr"/>
-      <c r="N422" t="inlineStr"/>
-      <c r="O422" t="inlineStr"/>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>Refacciones para Vehículos y Equipos de Transporte</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0421-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17498,10 +18298,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
-      <c r="G423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr">
@@ -17511,9 +18327,21 @@
       </c>
       <c r="K423" t="inlineStr"/>
       <c r="L423" t="inlineStr"/>
-      <c r="M423" t="inlineStr"/>
-      <c r="N423" t="inlineStr"/>
-      <c r="O423" t="inlineStr"/>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>Material Eléctrico</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Tula Tepeji</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0422-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O452"/>
+  <dimension ref="A1:O456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16124,8 +16124,16 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
-      <c r="E389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr"/>
       <c r="H389" t="inlineStr"/>
@@ -16145,9 +16153,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr"/>
-      <c r="N389" t="inlineStr"/>
-      <c r="O389" t="inlineStr"/>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos, Equipos y Aparatos de Comunicación y Telecomunicación, Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>la Subsecretaría del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia C5i de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0388-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -16165,10 +16185,26 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
-      <c r="G390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
       <c r="J390" t="inlineStr">
@@ -16186,9 +16222,21 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr"/>
-      <c r="N390" t="inlineStr"/>
-      <c r="O390" t="inlineStr"/>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>Asignación de Combustible Mediante Monederos Electrónicos</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0389-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -16206,10 +16254,26 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
-      <c r="G391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
       <c r="J391" t="inlineStr">
@@ -16219,9 +16283,21 @@
       </c>
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
-      <c r="M391" t="inlineStr"/>
-      <c r="N391" t="inlineStr"/>
-      <c r="O391" t="inlineStr"/>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo en conjunto con la Secretaría de Seguridad Pública del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0390-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16239,10 +16315,26 @@
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
-      <c r="G392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
       <c r="J392" t="inlineStr">
@@ -16260,9 +16352,21 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr"/>
-      <c r="N392" t="inlineStr"/>
-      <c r="O392" t="inlineStr"/>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>Asignación de Combustible Mediante Monederos Electrónicos</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0391-2026.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -17876,10 +17980,14 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="L416" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Libros de Texto</t>
@@ -17944,7 +18052,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="L417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Mantenimiento de Vehículos</t>
@@ -18009,7 +18121,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="L418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -18074,7 +18190,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="L419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Muebles, Excepto De Oficina y Estantería</t>
@@ -18203,7 +18323,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr"/>
       <c r="M421" t="inlineStr">
         <is>
@@ -18264,7 +18388,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr"/>
       <c r="M422" t="inlineStr">
         <is>
@@ -18325,7 +18453,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr"/>
       <c r="M423" t="inlineStr">
         <is>
@@ -18386,7 +18518,11 @@
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr"/>
       <c r="M424" t="inlineStr">
         <is>
@@ -18444,7 +18580,7 @@
       <c r="I425" t="inlineStr"/>
       <c r="J425" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K425" t="inlineStr"/>
@@ -19288,7 +19424,11 @@
       </c>
       <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K439" t="inlineStr"/>
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
@@ -19345,7 +19485,11 @@
       </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
@@ -19402,7 +19546,11 @@
       </c>
       <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
@@ -19459,7 +19607,11 @@
       </c>
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K442" t="inlineStr"/>
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
@@ -19630,7 +19782,11 @@
       </c>
       <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K445" t="inlineStr"/>
       <c r="L445" t="inlineStr"/>
       <c r="M445" t="inlineStr">
@@ -19744,7 +19900,11 @@
       </c>
       <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
       <c r="K447" t="inlineStr"/>
       <c r="L447" t="inlineStr"/>
       <c r="M447" t="inlineStr">
@@ -20048,6 +20208,234 @@
         </is>
       </c>
     </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0452-2026</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0452-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0453-2026</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Servicio de Creatividad, Diseño, Preproducción, Producción y Postproducción de Publicidad para el fortalecimiento de la Comunicación Institucional</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>la Dirección de Comunicación Social de la Secretaría de Desarrollo Económico del Poder Ejecutivo del Estado de Hidalgo y Dirección General de Atención y Vinculación Institucional de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0453-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0454-2026</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Servicio de Rider</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0454-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0455-2026</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Arrendamiento de Maquinaria, Otros Equipos y Herramientas, Arrendamiento de Vehículos y Equipo de Transporte</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0455-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O456"/>
+  <dimension ref="A1:O462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18328,7 +18328,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="L421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Servicios de Telecomunicaciones</t>
@@ -18393,7 +18397,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="L422" t="inlineStr"/>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Refacciones para Vehículos y Equipos de Transporte</t>
@@ -18523,7 +18531,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr"/>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Activos Intangibles (Sistema Integral de Enseñanza, aprendizaje y certificación del idioma inglés)</t>
@@ -18644,7 +18656,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr"/>
       <c r="M426" t="inlineStr">
         <is>
@@ -18705,7 +18721,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr"/>
       <c r="M427" t="inlineStr">
         <is>
@@ -18766,7 +18786,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr">
         <is>
@@ -18827,7 +18851,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr">
         <is>
@@ -18888,7 +18916,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr">
         <is>
@@ -18949,7 +18981,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr"/>
       <c r="M431" t="inlineStr">
         <is>
@@ -19002,7 +19038,11 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr"/>
       <c r="M432" t="inlineStr">
         <is>
@@ -19668,7 +19708,11 @@
       </c>
       <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
@@ -19725,7 +19769,11 @@
       </c>
       <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K444" t="inlineStr"/>
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
@@ -19843,7 +19891,11 @@
       </c>
       <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K446" t="inlineStr"/>
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
@@ -19961,7 +20013,11 @@
       </c>
       <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr"/>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
@@ -20018,7 +20074,11 @@
       </c>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
       <c r="M449" t="inlineStr">
@@ -20075,7 +20135,11 @@
       </c>
       <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
       <c r="K450" t="inlineStr"/>
       <c r="L450" t="inlineStr"/>
       <c r="M450" t="inlineStr">
@@ -20436,6 +20500,348 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0456-2026</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0456-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0457-2026</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0457-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0458-2026</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0458-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0459-2026</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>la Dirección de Asistencia Social del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0459-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0460-2026</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Material de Aseo Personal</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>el Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0460-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0461-2026</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Vehículos</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0461-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O462"/>
+  <dimension ref="A1:O465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18661,7 +18661,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -18726,7 +18730,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Material de Oficina, Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Material de Limpieza</t>
@@ -18791,7 +18799,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Combustibles y Lubricantes para Vehículos y Equipos Terrestres, Refacciones para Vehículos y Equipos de Transporte</t>
@@ -18856,7 +18868,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Prendas de Seguridad y Protección Personal, Identificadores e Iconos de Señalización, Herramientas Menores</t>
@@ -18921,7 +18937,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Arrendamiento de Maquinaria, Otros Equipos y Herramientas</t>
@@ -18986,7 +19006,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Prendas de Seguridad y Protección Personal</t>
@@ -19043,7 +19067,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="L432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Uniformes Escolares</t>
@@ -19103,7 +19131,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr"/>
       <c r="M433" t="inlineStr">
         <is>
@@ -19164,7 +19196,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr">
         <is>
@@ -19195,7 +19231,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -19225,7 +19261,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr">
         <is>
@@ -19286,7 +19326,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr">
         <is>
@@ -19347,7 +19391,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr">
         <is>
@@ -19408,7 +19456,11 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr">
         <is>
@@ -19832,11 +19884,19 @@
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Servicio de Fumigación</t>
@@ -19957,8 +20017,16 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Servicio de Fumigación</t>
@@ -20196,7 +20264,11 @@
       </c>
       <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr"/>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
@@ -20253,7 +20325,11 @@
       </c>
       <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
       <c r="K452" t="inlineStr"/>
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
@@ -20842,6 +20918,177 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0462-2026</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Activos Intangibles (Sistema Integral de Enseñanza, aprendizaje y certificación del idioma inglés)</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>el Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0462-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0463-2026</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0463-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0464-2026</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0464-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O465"/>
+  <dimension ref="A1:O471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18595,7 +18595,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr"/>
       <c r="M425" t="inlineStr">
         <is>
@@ -19136,7 +19140,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Asignación de Combustible a través de Monederos Electrónicos</t>
@@ -19266,7 +19274,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="L435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Material Eléctrico, Artículos Metálicos para la Construcción</t>
@@ -19331,7 +19343,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="L436" t="inlineStr"/>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Artículos Metálicos para la Construcción, Otros Materiales y Artículos de Construcción y Reparación, Identificadores e Iconos De Señalización</t>
@@ -19461,7 +19477,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir</t>
@@ -19518,7 +19538,7 @@
       <c r="I439" t="inlineStr"/>
       <c r="J439" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="K439" t="inlineStr"/>
@@ -19582,7 +19602,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr"/>
       <c r="M440" t="inlineStr">
         <is>
@@ -19643,7 +19667,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr"/>
       <c r="M441" t="inlineStr">
         <is>
@@ -19704,7 +19732,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr"/>
       <c r="M442" t="inlineStr">
         <is>
@@ -20024,7 +20056,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -20147,8 +20179,16 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Otros Arrendamientos para el evento “Viviendo en Plenitud”</t>
@@ -20208,8 +20248,16 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Servicio de Alimentos y Servicio de Impresiones para el evento “Viviendo en Plenitud”</t>
@@ -20386,7 +20434,11 @@
       </c>
       <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr"/>
-      <c r="J453" t="inlineStr"/>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr">
@@ -20443,7 +20495,11 @@
       </c>
       <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
@@ -20500,7 +20556,11 @@
       </c>
       <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="K455" t="inlineStr"/>
       <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
@@ -20557,7 +20617,11 @@
       </c>
       <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="K456" t="inlineStr"/>
       <c r="L456" t="inlineStr"/>
       <c r="M456" t="inlineStr">
@@ -21089,6 +21153,348 @@
         </is>
       </c>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0465-2026</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>el Centro de Rehabilitación Integral Hidalgo y Centros de Rehabilitación Integral Regionales del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0465-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0466-2026</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>los Centros de Rehabilitación Integral Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0466-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0467-2026</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Vestuario, Uniformes</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>la Dirección de Protección a la Niñez y Adolescencia del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0467-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0468-2026</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0468-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0469-2026</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>la Dirección General de Servicios Generales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0469-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0470-2026</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>la Dirección General de Servicios Generales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0470-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O471"/>
+  <dimension ref="A1:O478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -19607,7 +19607,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="L440" t="inlineStr"/>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Servicios de Acceso de Internet, Redes y Procesamiento de Información</t>
@@ -19672,7 +19676,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="L441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -19737,7 +19745,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="L442" t="inlineStr"/>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -19797,7 +19809,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
@@ -19858,7 +19874,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr"/>
       <c r="M444" t="inlineStr">
         <is>
@@ -19988,7 +20008,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr"/>
       <c r="M446" t="inlineStr">
         <is>
@@ -20051,7 +20075,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -20118,7 +20142,11 @@
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr"/>
       <c r="M448" t="inlineStr">
         <is>
@@ -20678,7 +20706,11 @@
       </c>
       <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K457" t="inlineStr"/>
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr">
@@ -20735,7 +20767,11 @@
       </c>
       <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K458" t="inlineStr"/>
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr">
@@ -20792,7 +20828,11 @@
       </c>
       <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K459" t="inlineStr"/>
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr">
@@ -20849,7 +20889,11 @@
       </c>
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr">
@@ -20906,7 +20950,11 @@
       </c>
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr">
@@ -20963,7 +21011,11 @@
       </c>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
@@ -21020,7 +21072,11 @@
       </c>
       <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
       <c r="K463" t="inlineStr"/>
       <c r="L463" t="inlineStr"/>
       <c r="M463" t="inlineStr">
@@ -21495,6 +21551,405 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0471-2026</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>Servicios Integrales de Telecomunicaciones y Redes de Transporte de Información</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0471-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0472-2026</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Servicios de Telecomunicaciones</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0472-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0473-2026</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Arrendamiento de Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0473-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0474-2026</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0474-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0475-2026</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0475-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0476-2026</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>Equipamiento de la Banda Sinfónica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>la Dirección General de Vinculación, Programación y Difusión Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0476-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0477-2026</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0477-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O478"/>
+  <dimension ref="A1:O484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18600,7 +18600,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="L425" t="inlineStr"/>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -19814,7 +19818,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr"/>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo (Segundo Procedimiento)</t>
@@ -20013,7 +20021,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr"/>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros de Laboratorio, Refacciones y Accesorios Menores de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -20345,7 +20357,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr"/>
       <c r="M451" t="inlineStr">
         <is>
@@ -20406,7 +20422,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
@@ -20464,7 +20484,7 @@
       <c r="I453" t="inlineStr"/>
       <c r="J453" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="K453" t="inlineStr"/>
@@ -21133,7 +21153,11 @@
       </c>
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr">
@@ -21190,7 +21214,11 @@
       </c>
       <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
       <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
@@ -21950,6 +21978,348 @@
         </is>
       </c>
     </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0478-2026</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Materiales para el Mantenimiento de Señalizaciones (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0478-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0479-2026</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>Artículos Metálicos para la Construcción, Otros Materiales y Artículos de Construcción y Reparación, Identificadores e Iconos De Señalización (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0479-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0480-2026</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0480-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0481-2026</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0481-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0482-2026</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Servicios Financieros y Bancarios</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Juventud</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0482-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0483-2026</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Equipamiento de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>el Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0483-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O484"/>
+  <dimension ref="A1:O489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -19545,7 +19545,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr">
         <is>
@@ -20362,7 +20366,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr"/>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Equipo Médico y de Laboratorio (Electromiógrafo)</t>
@@ -20548,7 +20556,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr">
         <is>
@@ -20609,7 +20621,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr"/>
       <c r="M455" t="inlineStr">
         <is>
@@ -20670,7 +20686,11 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr"/>
       <c r="M456" t="inlineStr">
         <is>
@@ -21097,8 +21117,16 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Activos Intangibles (Sistema Integral de Enseñanza, aprendizaje y certificación del idioma inglés)</t>
@@ -21275,7 +21303,11 @@
       </c>
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr"/>
       <c r="M466" t="inlineStr">
@@ -21332,7 +21364,11 @@
       </c>
       <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
-      <c r="J467" t="inlineStr"/>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K467" t="inlineStr"/>
       <c r="L467" t="inlineStr"/>
       <c r="M467" t="inlineStr">
@@ -21389,7 +21425,11 @@
       </c>
       <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
@@ -21446,7 +21486,11 @@
       </c>
       <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr">
@@ -21503,7 +21547,11 @@
       </c>
       <c r="H470" t="inlineStr"/>
       <c r="I470" t="inlineStr"/>
-      <c r="J470" t="inlineStr"/>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K470" t="inlineStr"/>
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr">
@@ -21560,7 +21608,11 @@
       </c>
       <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr"/>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
       <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr">
@@ -22320,6 +22372,291 @@
         </is>
       </c>
     </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0484-2026</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>la Subsecretaria del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación, e Inteligencia de la Secretaría de Seguridad Pública del Poder Ejecutivo del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0484-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0485-2026</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>Mobiliario y Equipamiento de Oficina</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0485-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0486-2026</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0486-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0487-2026</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Bienes Informáticos, Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0487-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0488-2026</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Huertos familiares)</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>la Dirección General de Agricultura de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0488-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O489"/>
+  <dimension ref="A1:O493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -20561,7 +20561,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr"/>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Servicio de Creatividad, Diseño, Preproducción, Producción y Postproducción de Publicidad para el fortalecimiento de la Comunicación Institucional</t>
@@ -20626,7 +20630,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr"/>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Servicio de Rider</t>
@@ -20691,7 +20699,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L456" t="inlineStr"/>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Arrendamiento de Maquinaria, Otros Equipos y Herramientas, Arrendamiento de Vehículos y Equipo de Transporte</t>
@@ -20751,7 +20763,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr"/>
       <c r="M457" t="inlineStr">
         <is>
@@ -20812,7 +20828,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr">
         <is>
@@ -20934,7 +20954,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr">
         <is>
@@ -20995,7 +21019,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr"/>
       <c r="M461" t="inlineStr">
         <is>
@@ -21056,7 +21084,11 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr"/>
       <c r="M462" t="inlineStr">
         <is>
@@ -21669,7 +21701,11 @@
       </c>
       <c r="H472" t="inlineStr"/>
       <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr"/>
       <c r="M472" t="inlineStr">
@@ -21726,7 +21762,11 @@
       </c>
       <c r="H473" t="inlineStr"/>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K473" t="inlineStr"/>
       <c r="L473" t="inlineStr"/>
       <c r="M473" t="inlineStr">
@@ -21783,7 +21823,11 @@
       </c>
       <c r="H474" t="inlineStr"/>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr"/>
       <c r="M474" t="inlineStr">
@@ -21840,7 +21884,11 @@
       </c>
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr"/>
       <c r="M475" t="inlineStr">
@@ -21897,7 +21945,11 @@
       </c>
       <c r="H476" t="inlineStr"/>
       <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr"/>
       <c r="M476" t="inlineStr">
@@ -21954,7 +22006,11 @@
       </c>
       <c r="H477" t="inlineStr"/>
       <c r="I477" t="inlineStr"/>
-      <c r="J477" t="inlineStr"/>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K477" t="inlineStr"/>
       <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr">
@@ -22011,7 +22067,11 @@
       </c>
       <c r="H478" t="inlineStr"/>
       <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr"/>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="K478" t="inlineStr"/>
       <c r="L478" t="inlineStr"/>
       <c r="M478" t="inlineStr">
@@ -22657,6 +22717,234 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0489-2026</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>Prendas de Seguridad y Protección Personal</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención, Control y Combate de Incendios Forestales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0489-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0490-2026</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>Servicios de Creatividad, Preproducción y Producción de Publicidad, Excepto Internet</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>la Dirección General de Promoción y Mercadotecnia de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0490-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0491-2026</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>la Subsecretaría del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia C5i de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0491-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0492-2026</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0492-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O493"/>
+  <dimension ref="A1:O497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19550,7 +19550,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="L439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Servicios Integrales</t>
@@ -20495,7 +20499,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr">
         <is>
@@ -20833,7 +20841,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="L458" t="inlineStr"/>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -20890,7 +20902,7 @@
       <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K459" t="inlineStr"/>
@@ -20959,7 +20971,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr"/>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -21024,7 +21040,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr"/>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Material de Aseo Personal</t>
@@ -21218,7 +21238,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr"/>
       <c r="M464" t="inlineStr">
         <is>
@@ -21279,7 +21303,11 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr">
         <is>
@@ -22128,7 +22156,11 @@
       </c>
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
       <c r="M479" t="inlineStr">
@@ -22185,7 +22217,11 @@
       </c>
       <c r="H480" t="inlineStr"/>
       <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr">
@@ -22242,7 +22278,11 @@
       </c>
       <c r="H481" t="inlineStr"/>
       <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
       <c r="M481" t="inlineStr">
@@ -22299,7 +22339,11 @@
       </c>
       <c r="H482" t="inlineStr"/>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr">
@@ -22356,7 +22400,11 @@
       </c>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr"/>
       <c r="M483" t="inlineStr">
@@ -22413,7 +22461,11 @@
       </c>
       <c r="H484" t="inlineStr"/>
       <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr"/>
       <c r="M484" t="inlineStr">
@@ -22945,6 +22997,234 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0493-2026</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Terneras)</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0493-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0494-2026</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Equipo de café)</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0494-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0495-2026</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+      <c r="J496" t="inlineStr"/>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Material Didáctico, Material de Limpieza, Material de Oficina, Consumibles para el Procesamiento en equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>el Consejo Estatal para la Cultura y las Artes de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0495-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0496-2026</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Vestuario, Uniformes y Blancos</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Humanos de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0496-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O497"/>
+  <dimension ref="A1:O505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20504,7 +20504,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="L453" t="inlineStr"/>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Seguros</t>
@@ -20776,7 +20780,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr"/>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -20973,7 +20981,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -21109,7 +21117,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr"/>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Mantenimiento de Vehículos</t>
@@ -21243,7 +21255,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr"/>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -21308,7 +21324,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr"/>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -21368,7 +21388,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr"/>
       <c r="M466" t="inlineStr">
         <is>
@@ -21429,7 +21453,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr"/>
       <c r="M467" t="inlineStr">
         <is>
@@ -21490,7 +21518,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr"/>
       <c r="M468" t="inlineStr">
         <is>
@@ -21551,7 +21583,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr"/>
       <c r="M469" t="inlineStr">
         <is>
@@ -21612,7 +21648,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr">
         <is>
@@ -21673,7 +21713,11 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr">
         <is>
@@ -22522,7 +22566,11 @@
       </c>
       <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="K485" t="inlineStr"/>
       <c r="L485" t="inlineStr"/>
       <c r="M485" t="inlineStr">
@@ -22579,7 +22627,11 @@
       </c>
       <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="K486" t="inlineStr"/>
       <c r="L486" t="inlineStr"/>
       <c r="M486" t="inlineStr">
@@ -22636,7 +22688,11 @@
       </c>
       <c r="H487" t="inlineStr"/>
       <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="K487" t="inlineStr"/>
       <c r="L487" t="inlineStr"/>
       <c r="M487" t="inlineStr">
@@ -22693,7 +22749,11 @@
       </c>
       <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
-      <c r="J488" t="inlineStr"/>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="K488" t="inlineStr"/>
       <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr">
@@ -22750,7 +22810,11 @@
       </c>
       <c r="H489" t="inlineStr"/>
       <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
       <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr">
@@ -23225,6 +23289,462 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0497-2026</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>los Centros de Rehabilitación Integral Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0497-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0498-2026</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+      <c r="J499" t="inlineStr"/>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0498-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0499-2026</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Materiales Y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0499-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0500-2026</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0500-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0501-2026</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Plaguicidas, Abonos y Fertilizantes, Fibras Sintéticas, Hules, Plásticos y Derivados, Maquinaria y Equipo Agropecuario, Equipo de Construcción</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0501-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0502-2026</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>Fibras Sintéticas, Hules, Plásticos y Derivados</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0502-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0503-2026</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Servicios de Creatividad, Preproducción y Producción de Publicidad, Excepto Internet</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>la Subdirección de Comunicación Social de la Secretaría de Salud del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0503-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0504-2026</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+      <c r="J505" t="inlineStr"/>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0504-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O505"/>
+  <dimension ref="A1:O511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -20910,7 +20910,7 @@
       <c r="I459" t="inlineStr"/>
       <c r="J459" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K459" t="inlineStr"/>
@@ -21458,7 +21458,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr"/>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -21523,7 +21527,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr"/>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t>Vestuario, Uniformes</t>
@@ -21588,7 +21596,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr"/>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -21653,7 +21665,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr"/>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -21718,7 +21734,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr"/>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo (Segundo Procedimiento)</t>
@@ -21778,8 +21798,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
-      <c r="L472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t>Servicios Integrales de Telecomunicaciones y Redes de Transporte de Información</t>
@@ -21839,8 +21867,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
-      <c r="L473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t>Servicios de Telecomunicaciones</t>
@@ -21900,8 +21936,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t>Arrendamiento de Activos Intangibles</t>
@@ -21958,7 +22002,7 @@
       <c r="I475" t="inlineStr"/>
       <c r="J475" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K475" t="inlineStr"/>
@@ -22019,7 +22063,7 @@
       <c r="I476" t="inlineStr"/>
       <c r="J476" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="K476" t="inlineStr"/>
@@ -22083,7 +22127,11 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr"/>
       <c r="M477" t="inlineStr">
         <is>
@@ -22144,8 +22192,16 @@
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
-      <c r="L478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
@@ -22205,7 +22261,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr"/>
       <c r="M479" t="inlineStr">
         <is>
@@ -22266,7 +22326,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr"/>
       <c r="M480" t="inlineStr">
         <is>
@@ -22327,7 +22391,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr"/>
       <c r="M481" t="inlineStr">
         <is>
@@ -22388,7 +22456,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr">
         <is>
@@ -22449,7 +22521,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr"/>
       <c r="M483" t="inlineStr">
         <is>
@@ -22510,7 +22586,11 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr"/>
       <c r="M484" t="inlineStr">
         <is>
@@ -22871,7 +22951,11 @@
       </c>
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr">
@@ -22928,7 +23012,11 @@
       </c>
       <c r="H491" t="inlineStr"/>
       <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr"/>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr">
@@ -22985,7 +23073,11 @@
       </c>
       <c r="H492" t="inlineStr"/>
       <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr"/>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="K492" t="inlineStr"/>
       <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr">
@@ -23042,7 +23134,11 @@
       </c>
       <c r="H493" t="inlineStr"/>
       <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="K493" t="inlineStr"/>
       <c r="L493" t="inlineStr"/>
       <c r="M493" t="inlineStr">
@@ -23099,7 +23195,11 @@
       </c>
       <c r="H494" t="inlineStr"/>
       <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="K494" t="inlineStr"/>
       <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr">
@@ -23156,7 +23256,11 @@
       </c>
       <c r="H495" t="inlineStr"/>
       <c r="I495" t="inlineStr"/>
-      <c r="J495" t="inlineStr"/>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="K495" t="inlineStr"/>
       <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr">
@@ -23213,7 +23317,11 @@
       </c>
       <c r="H496" t="inlineStr"/>
       <c r="I496" t="inlineStr"/>
-      <c r="J496" t="inlineStr"/>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr">
@@ -23745,6 +23853,348 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0505-2026</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+      <c r="J506" t="inlineStr"/>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>la Dirección General de Gestión de Calidad del Aire, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0505-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0506-2026</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+      <c r="J507" t="inlineStr"/>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>la Dirección General de Cuencas y Planeación Hídrica, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0506-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0507-2026</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros Médicos</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0507-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0508-2026</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+      <c r="J509" t="inlineStr"/>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>Servicios Integrales (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0508-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0509-2026</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0509-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0510-2026</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+      <c r="J511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Estudio e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0510-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O511"/>
+  <dimension ref="A1:O517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -22266,7 +22266,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr"/>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Materiales para el Mantenimiento de Señalizaciones (Segundo Procedimiento)</t>
@@ -22331,7 +22335,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr"/>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t>Artículos Metálicos para la Construcción, Otros Materiales y Artículos de Construcción y Reparación, Identificadores e Iconos De Señalización (Segundo Procedimiento)</t>
@@ -22396,7 +22404,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr"/>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -22461,7 +22473,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr"/>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -22526,7 +22542,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr"/>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t>Servicios Financieros y Bancarios</t>
@@ -22591,7 +22611,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="L484" t="inlineStr"/>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t>Equipamiento de Laboratorio</t>
@@ -22651,7 +22675,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr"/>
       <c r="M485" t="inlineStr">
         <is>
@@ -22712,7 +22740,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr"/>
       <c r="M486" t="inlineStr">
         <is>
@@ -22770,7 +22802,7 @@
       <c r="I487" t="inlineStr"/>
       <c r="J487" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="K487" t="inlineStr"/>
@@ -22834,7 +22866,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr"/>
       <c r="M488" t="inlineStr">
         <is>
@@ -22895,7 +22931,11 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr"/>
       <c r="M489" t="inlineStr">
         <is>
@@ -23378,7 +23418,11 @@
       </c>
       <c r="H497" t="inlineStr"/>
       <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K497" t="inlineStr"/>
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr">
@@ -23435,7 +23479,11 @@
       </c>
       <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr"/>
-      <c r="J498" t="inlineStr"/>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K498" t="inlineStr"/>
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr">
@@ -23492,7 +23540,11 @@
       </c>
       <c r="H499" t="inlineStr"/>
       <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr"/>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr">
@@ -23549,7 +23601,11 @@
       </c>
       <c r="H500" t="inlineStr"/>
       <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr"/>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K500" t="inlineStr"/>
       <c r="L500" t="inlineStr"/>
       <c r="M500" t="inlineStr">
@@ -23606,7 +23662,11 @@
       </c>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr"/>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K501" t="inlineStr"/>
       <c r="L501" t="inlineStr"/>
       <c r="M501" t="inlineStr">
@@ -23663,7 +23723,11 @@
       </c>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr"/>
       <c r="M502" t="inlineStr">
@@ -23720,7 +23784,11 @@
       </c>
       <c r="H503" t="inlineStr"/>
       <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr"/>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K503" t="inlineStr"/>
       <c r="L503" t="inlineStr"/>
       <c r="M503" t="inlineStr">
@@ -23777,7 +23845,11 @@
       </c>
       <c r="H504" t="inlineStr"/>
       <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K504" t="inlineStr"/>
       <c r="L504" t="inlineStr"/>
       <c r="M504" t="inlineStr">
@@ -24195,6 +24267,348 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0511-2026</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+      <c r="J512" t="inlineStr"/>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0511-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0512-2026</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>la Subsecretaría del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia C5i de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0512-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0513-2026</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+      <c r="J514" t="inlineStr"/>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros Médicos</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0513-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0514-2026</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+      <c r="J515" t="inlineStr"/>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0514-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0515-2026</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+      <c r="J516" t="inlineStr"/>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>Herramientas Menores</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0515-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0516-2026</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+      <c r="J517" t="inlineStr"/>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>Conservación y Mantenimiento Menor de Inmuebles</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>la Dirección General de Servicios Generales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0516-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O517"/>
+  <dimension ref="A1:O523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22936,7 +22936,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr"/>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Huertos familiares)</t>
@@ -23906,7 +23910,11 @@
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr"/>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
       <c r="M505" t="inlineStr">
@@ -24248,7 +24256,11 @@
       </c>
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr"/>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
       <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr"/>
       <c r="M511" t="inlineStr">
@@ -24609,6 +24621,348 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0517-2026</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+      <c r="J518" t="inlineStr"/>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios Y Suministros Médicos</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Pachuca</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0517-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0518-2026</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+      <c r="J519" t="inlineStr"/>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones (PIMUS de Huejutla de Reyes, PIMUS de Ixmiquilpan)</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>la Dirección General de Movilidad Sustentable de la Secretaría de Movilidad y Transporte del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0518-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0519-2026</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+      <c r="J520" t="inlineStr"/>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>Equipo educativo para el Laboratorio de Innovación Agrícola Sustentable</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>la Subdirección de Servicios Administrativos del Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0519-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0520-2026</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+      <c r="J521" t="inlineStr"/>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Vientre Ovino)</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0520-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0521-2026</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+      <c r="J522" t="inlineStr"/>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Mobiliario y Equipo de Administración, Educacional y Recreativo, Impresiones y Publicaciones Oficiales</t>
+        </is>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>la Dirección General de Fomento Artesanal de la Secretaría de Bienestar e Inclusión Social, del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0521-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0522-2026</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+      <c r="J523" t="inlineStr"/>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Otros Arrendamientos</t>
+        </is>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>la Dirección General de Fomento Artesanal de la Secretaría de Bienestar e Inclusión Social, del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0522-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O523"/>
+  <dimension ref="A1:O529"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20913,7 +20913,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr">
         <is>
@@ -22005,7 +22009,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr"/>
       <c r="M475" t="inlineStr">
         <is>
@@ -22066,7 +22074,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr"/>
       <c r="M476" t="inlineStr">
         <is>
@@ -22680,7 +22692,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr"/>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -22745,7 +22761,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr"/>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t>Mobiliario y Equipamiento de Oficina</t>
@@ -23000,7 +23020,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr"/>
       <c r="M490" t="inlineStr">
         <is>
@@ -23061,7 +23085,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr"/>
       <c r="M491" t="inlineStr">
         <is>
@@ -23122,7 +23150,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr"/>
       <c r="M492" t="inlineStr">
         <is>
@@ -23183,7 +23215,11 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr"/>
       <c r="M493" t="inlineStr">
         <is>
@@ -23971,7 +24007,11 @@
       </c>
       <c r="H506" t="inlineStr"/>
       <c r="I506" t="inlineStr"/>
-      <c r="J506" t="inlineStr"/>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="K506" t="inlineStr"/>
       <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr">
@@ -24028,7 +24068,11 @@
       </c>
       <c r="H507" t="inlineStr"/>
       <c r="I507" t="inlineStr"/>
-      <c r="J507" t="inlineStr"/>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="K507" t="inlineStr"/>
       <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr">
@@ -24085,7 +24129,11 @@
       </c>
       <c r="H508" t="inlineStr"/>
       <c r="I508" t="inlineStr"/>
-      <c r="J508" t="inlineStr"/>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="K508" t="inlineStr"/>
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr">
@@ -24142,7 +24190,11 @@
       </c>
       <c r="H509" t="inlineStr"/>
       <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="K509" t="inlineStr"/>
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr">
@@ -24199,7 +24251,11 @@
       </c>
       <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr"/>
-      <c r="J510" t="inlineStr"/>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr">
@@ -24963,6 +25019,348 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0523-2026</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+      <c r="J524" t="inlineStr"/>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Equipamiento de la Orquesta Sinfónica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>la Dirección General de Vinculación, Programación y Difusión Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0523-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0524-2026</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+      <c r="J525" t="inlineStr"/>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>Ayudas Sociales A Personas</t>
+        </is>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0524-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0525-2026</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+      <c r="J526" t="inlineStr"/>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Plaguicidas, Abonos y Fertilizantes</t>
+        </is>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0525-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0526-2026</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+      <c r="J527" t="inlineStr"/>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Prendas de Protección para Seguridad Pública</t>
+        </is>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Operación Policial de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0526-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0527-2026</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Alimentación de Animales</t>
+        </is>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0527-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0528-2026</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Módulos de Invernadero)</t>
+        </is>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>la Dirección General de Desarrollo Rural de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0528-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O529"/>
+  <dimension ref="A1:O535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23025,7 +23025,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr"/>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t>Prendas de Seguridad y Protección Personal</t>
@@ -23090,7 +23094,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr"/>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t>Servicios de Creatividad, Preproducción y Producción de Publicidad, Excepto Internet</t>
@@ -23155,7 +23163,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="L492" t="inlineStr"/>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -23220,7 +23232,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="L493" t="inlineStr"/>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M493" t="inlineStr">
         <is>
           <t>Servicios Integrales</t>
@@ -23280,7 +23296,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr"/>
       <c r="M494" t="inlineStr">
         <is>
@@ -23341,7 +23361,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr"/>
       <c r="M495" t="inlineStr">
         <is>
@@ -23402,7 +23426,11 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr"/>
       <c r="M496" t="inlineStr">
         <is>
@@ -23463,7 +23491,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr">
         <is>
@@ -24317,8 +24349,16 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
-      <c r="L511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="M511" t="inlineStr">
         <is>
           <t>Estudio e Investigaciones</t>
@@ -24373,7 +24413,11 @@
       </c>
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="inlineStr"/>
-      <c r="J512" t="inlineStr"/>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K512" t="inlineStr"/>
       <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr">
@@ -24430,7 +24474,11 @@
       </c>
       <c r="H513" t="inlineStr"/>
       <c r="I513" t="inlineStr"/>
-      <c r="J513" t="inlineStr"/>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K513" t="inlineStr"/>
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr">
@@ -24487,7 +24535,11 @@
       </c>
       <c r="H514" t="inlineStr"/>
       <c r="I514" t="inlineStr"/>
-      <c r="J514" t="inlineStr"/>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K514" t="inlineStr"/>
       <c r="L514" t="inlineStr"/>
       <c r="M514" t="inlineStr">
@@ -24544,7 +24596,11 @@
       </c>
       <c r="H515" t="inlineStr"/>
       <c r="I515" t="inlineStr"/>
-      <c r="J515" t="inlineStr"/>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K515" t="inlineStr"/>
       <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr">
@@ -24601,7 +24657,11 @@
       </c>
       <c r="H516" t="inlineStr"/>
       <c r="I516" t="inlineStr"/>
-      <c r="J516" t="inlineStr"/>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
       <c r="M516" t="inlineStr">
@@ -24658,7 +24718,11 @@
       </c>
       <c r="H517" t="inlineStr"/>
       <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
       <c r="K517" t="inlineStr"/>
       <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
@@ -25361,6 +25425,348 @@
         </is>
       </c>
     </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0529-2026</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>Equipamiento para la asignación de espacios</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>la Dirección General de Fomento Artesanal de la Secretaría de Bienestar e Inclusión Social del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0529-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0530-2026</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Servicio de Mantenimiento de Maquinaria y Equipo en Inmuebles</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>el Consejo Estatal para la Cultura y las Artes de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0530-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0531-2026</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+      <c r="J532" t="inlineStr"/>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0531-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0532-2026</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Bienes Informáticos, Material Eléctrico</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0532-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0533-2026</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+      <c r="J534" t="inlineStr"/>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>Computadora de Escritorio</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0533-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0534-2026</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+      <c r="J535" t="inlineStr"/>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0534-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O535"/>
+  <dimension ref="A1:O542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22825,7 +22825,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr"/>
       <c r="M487" t="inlineStr">
         <is>
@@ -23301,7 +23305,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="L494" t="inlineStr"/>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="M494" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Terneras)</t>
@@ -23496,7 +23504,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="L497" t="inlineStr"/>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="M497" t="inlineStr">
         <is>
           <t>Vestuario, Uniformes y Blancos</t>
@@ -23556,7 +23568,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr">
         <is>
@@ -23617,7 +23633,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr">
         <is>
@@ -23678,7 +23698,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr"/>
       <c r="M500" t="inlineStr">
         <is>
@@ -23739,7 +23763,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr"/>
       <c r="M501" t="inlineStr">
         <is>
@@ -23800,7 +23828,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr"/>
       <c r="M502" t="inlineStr">
         <is>
@@ -23861,7 +23893,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr"/>
       <c r="M503" t="inlineStr">
         <is>
@@ -23983,7 +24019,11 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr"/>
       <c r="M505" t="inlineStr">
         <is>
@@ -24779,7 +24819,11 @@
       </c>
       <c r="H518" t="inlineStr"/>
       <c r="I518" t="inlineStr"/>
-      <c r="J518" t="inlineStr"/>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
@@ -24836,7 +24880,11 @@
       </c>
       <c r="H519" t="inlineStr"/>
       <c r="I519" t="inlineStr"/>
-      <c r="J519" t="inlineStr"/>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K519" t="inlineStr"/>
       <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr">
@@ -24893,7 +24941,11 @@
       </c>
       <c r="H520" t="inlineStr"/>
       <c r="I520" t="inlineStr"/>
-      <c r="J520" t="inlineStr"/>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K520" t="inlineStr"/>
       <c r="L520" t="inlineStr"/>
       <c r="M520" t="inlineStr">
@@ -24950,7 +25002,11 @@
       </c>
       <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr"/>
-      <c r="J521" t="inlineStr"/>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K521" t="inlineStr"/>
       <c r="L521" t="inlineStr"/>
       <c r="M521" t="inlineStr">
@@ -25007,7 +25063,11 @@
       </c>
       <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr"/>
-      <c r="J522" t="inlineStr"/>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K522" t="inlineStr"/>
       <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr">
@@ -25064,7 +25124,11 @@
       </c>
       <c r="H523" t="inlineStr"/>
       <c r="I523" t="inlineStr"/>
-      <c r="J523" t="inlineStr"/>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
@@ -25767,6 +25831,405 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0535-2026</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+      <c r="J536" t="inlineStr"/>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0535-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0536-2026</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+      <c r="J537" t="inlineStr"/>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas, Gastos de Oficina</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Francisco I. Madero</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0536-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0537-2026</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+      <c r="J538" t="inlineStr"/>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0537-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0538-2026</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+      <c r="J539" t="inlineStr"/>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0538-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0539-2026</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+      <c r="J540" t="inlineStr"/>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>la Dirección General de Servicios Generales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0539-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0540-2026</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+      <c r="J541" t="inlineStr"/>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0540-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0541-2026</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+      <c r="J542" t="inlineStr"/>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>Combustibles y Lubricantes para Vehículos y Equipos Terrestres</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0541-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O542"/>
+  <dimension ref="A1:O547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23439,7 +23439,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="L496" t="inlineStr"/>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M496" t="inlineStr">
         <is>
           <t>Material Didáctico, Material de Limpieza, Material de Oficina, Consumibles para el Procesamiento en equipos y Bienes Informáticos</t>
@@ -23573,7 +23577,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr"/>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M498" t="inlineStr">
         <is>
           <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (Segundo Procedimiento)</t>
@@ -23638,7 +23646,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr"/>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M499" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -23703,7 +23715,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L500" t="inlineStr"/>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M500" t="inlineStr">
         <is>
           <t>Materiales Y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -23768,7 +23784,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L501" t="inlineStr"/>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M501" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
@@ -23833,7 +23853,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L502" t="inlineStr"/>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M502" t="inlineStr">
         <is>
           <t>Plaguicidas, Abonos y Fertilizantes, Fibras Sintéticas, Hules, Plásticos y Derivados, Maquinaria y Equipo Agropecuario, Equipo de Construcción</t>
@@ -23898,7 +23922,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="L503" t="inlineStr"/>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M503" t="inlineStr">
         <is>
           <t>Fibras Sintéticas, Hules, Plásticos y Derivados</t>
@@ -24084,7 +24112,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr"/>
       <c r="M506" t="inlineStr">
         <is>
@@ -24145,7 +24177,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr"/>
       <c r="M507" t="inlineStr">
         <is>
@@ -24206,7 +24242,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr"/>
       <c r="M508" t="inlineStr">
         <is>
@@ -24267,7 +24307,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr"/>
       <c r="M509" t="inlineStr">
         <is>
@@ -24328,7 +24372,11 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr"/>
       <c r="M510" t="inlineStr">
         <is>
@@ -25185,7 +25233,11 @@
       </c>
       <c r="H524" t="inlineStr"/>
       <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="K524" t="inlineStr"/>
       <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
@@ -25242,7 +25294,11 @@
       </c>
       <c r="H525" t="inlineStr"/>
       <c r="I525" t="inlineStr"/>
-      <c r="J525" t="inlineStr"/>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="K525" t="inlineStr"/>
       <c r="L525" t="inlineStr"/>
       <c r="M525" t="inlineStr">
@@ -25299,7 +25355,11 @@
       </c>
       <c r="H526" t="inlineStr"/>
       <c r="I526" t="inlineStr"/>
-      <c r="J526" t="inlineStr"/>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K526" t="inlineStr"/>
       <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
@@ -25356,7 +25416,11 @@
       </c>
       <c r="H527" t="inlineStr"/>
       <c r="I527" t="inlineStr"/>
-      <c r="J527" t="inlineStr"/>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr"/>
       <c r="M527" t="inlineStr">
@@ -25413,7 +25477,11 @@
       </c>
       <c r="H528" t="inlineStr"/>
       <c r="I528" t="inlineStr"/>
-      <c r="J528" t="inlineStr"/>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K528" t="inlineStr"/>
       <c r="L528" t="inlineStr"/>
       <c r="M528" t="inlineStr">
@@ -25470,7 +25538,11 @@
       </c>
       <c r="H529" t="inlineStr"/>
       <c r="I529" t="inlineStr"/>
-      <c r="J529" t="inlineStr"/>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K529" t="inlineStr"/>
       <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr">
@@ -26230,6 +26302,291 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0542-2026</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+      <c r="J543" t="inlineStr"/>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>Servicios Integrales de Telecomunicaciones y Redes de Transporte de Información</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0542-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0543-2026</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+      <c r="J544" t="inlineStr"/>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>Servicios de Internet</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0543-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0544-2026</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+      <c r="J545" t="inlineStr"/>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>Servicios Legales</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>el Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0544-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0545-2026</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+      <c r="J546" t="inlineStr"/>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0545-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0546-2026</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+      <c r="J547" t="inlineStr"/>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Maquinaria y Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0546-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24117,7 +24117,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr"/>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="M506" t="inlineStr">
         <is>
           <t>Sustancias Químicas</t>
@@ -24182,7 +24186,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr"/>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="M507" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo (Tercer Procedimiento)</t>
@@ -24377,7 +24385,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="L510" t="inlineStr"/>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="M510" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -24503,7 +24515,7 @@
       <c r="I512" t="inlineStr"/>
       <c r="J512" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K512" t="inlineStr"/>
@@ -24567,7 +24579,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr"/>
       <c r="M513" t="inlineStr">
         <is>
@@ -24628,7 +24644,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr"/>
       <c r="M514" t="inlineStr">
         <is>
@@ -24686,7 +24706,7 @@
       <c r="I515" t="inlineStr"/>
       <c r="J515" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K515" t="inlineStr"/>
@@ -24750,7 +24770,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr"/>
       <c r="M516" t="inlineStr">
         <is>
@@ -24811,7 +24835,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
         <is>
@@ -25599,7 +25627,11 @@
       </c>
       <c r="H530" t="inlineStr"/>
       <c r="I530" t="inlineStr"/>
-      <c r="J530" t="inlineStr"/>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K530" t="inlineStr"/>
       <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
@@ -25656,7 +25688,11 @@
       </c>
       <c r="H531" t="inlineStr"/>
       <c r="I531" t="inlineStr"/>
-      <c r="J531" t="inlineStr"/>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K531" t="inlineStr"/>
       <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
@@ -25713,7 +25749,11 @@
       </c>
       <c r="H532" t="inlineStr"/>
       <c r="I532" t="inlineStr"/>
-      <c r="J532" t="inlineStr"/>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K532" t="inlineStr"/>
       <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr">
@@ -25770,7 +25810,11 @@
       </c>
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr"/>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr">
@@ -25827,7 +25871,11 @@
       </c>
       <c r="H534" t="inlineStr"/>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr">
@@ -25884,7 +25932,11 @@
       </c>
       <c r="H535" t="inlineStr"/>
       <c r="I535" t="inlineStr"/>
-      <c r="J535" t="inlineStr"/>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K535" t="inlineStr"/>
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr">
@@ -26587,6 +26639,291 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0547-2026</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+      <c r="J548" t="inlineStr"/>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>los Centros de Rehabilitación Integral Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0547-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0548-2026</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+      <c r="J549" t="inlineStr"/>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0548-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0549-2026</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+      <c r="J550" t="inlineStr"/>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>la Dirección de Informática del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0549-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0550-2026</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+      <c r="J551" t="inlineStr"/>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Donativos a Entes Públicos Estatales y Municipales</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>el Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0550-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0551-2026</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
+      <c r="J552" t="inlineStr"/>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Seguro de Accidentes Escolares</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0551-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O552"/>
+  <dimension ref="A1:O557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24255,7 +24255,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr"/>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="M508" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros Médicos</t>
@@ -24584,7 +24588,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr"/>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="M513" t="inlineStr">
         <is>
           <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
@@ -24649,7 +24657,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr"/>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="M514" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros Médicos</t>
@@ -24775,7 +24787,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="L516" t="inlineStr"/>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="M516" t="inlineStr">
         <is>
           <t>Herramientas Menores</t>
@@ -24900,7 +24916,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr"/>
       <c r="M518" t="inlineStr">
         <is>
@@ -24961,7 +24981,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr"/>
       <c r="M519" t="inlineStr">
         <is>
@@ -25022,7 +25046,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr"/>
       <c r="M520" t="inlineStr">
         <is>
@@ -25083,7 +25111,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr"/>
       <c r="M521" t="inlineStr">
         <is>
@@ -25144,7 +25176,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr"/>
       <c r="M522" t="inlineStr">
         <is>
@@ -25205,7 +25241,11 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr"/>
       <c r="M523" t="inlineStr">
         <is>
@@ -25993,7 +26033,11 @@
       </c>
       <c r="H536" t="inlineStr"/>
       <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr"/>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr">
@@ -26050,7 +26094,11 @@
       </c>
       <c r="H537" t="inlineStr"/>
       <c r="I537" t="inlineStr"/>
-      <c r="J537" t="inlineStr"/>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K537" t="inlineStr"/>
       <c r="L537" t="inlineStr"/>
       <c r="M537" t="inlineStr">
@@ -26107,7 +26155,11 @@
       </c>
       <c r="H538" t="inlineStr"/>
       <c r="I538" t="inlineStr"/>
-      <c r="J538" t="inlineStr"/>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K538" t="inlineStr"/>
       <c r="L538" t="inlineStr"/>
       <c r="M538" t="inlineStr">
@@ -26164,7 +26216,11 @@
       </c>
       <c r="H539" t="inlineStr"/>
       <c r="I539" t="inlineStr"/>
-      <c r="J539" t="inlineStr"/>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr">
@@ -26221,7 +26277,11 @@
       </c>
       <c r="H540" t="inlineStr"/>
       <c r="I540" t="inlineStr"/>
-      <c r="J540" t="inlineStr"/>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr"/>
       <c r="M540" t="inlineStr">
@@ -26278,7 +26338,11 @@
       </c>
       <c r="H541" t="inlineStr"/>
       <c r="I541" t="inlineStr"/>
-      <c r="J541" t="inlineStr"/>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K541" t="inlineStr"/>
       <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr">
@@ -26335,7 +26399,11 @@
       </c>
       <c r="H542" t="inlineStr"/>
       <c r="I542" t="inlineStr"/>
-      <c r="J542" t="inlineStr"/>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="K542" t="inlineStr"/>
       <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr">
@@ -26924,6 +26992,291 @@
         </is>
       </c>
     </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0552-2026</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+      <c r="J553" t="inlineStr"/>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>Equipamiento Especializado para la Elaboración y Supervisión de Proyectos</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0552-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0553-2026</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+      <c r="J554" t="inlineStr"/>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0553-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0554-2026</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+      <c r="J555" t="inlineStr"/>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>Utensilios para el Servicio de Alimentación</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0554-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0555-2026</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+      <c r="J556" t="inlineStr"/>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Cría de Trucha Arcoíris)</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>la Dirección de Acuacultura y Pesca de la Dirección General de Silvicultura, Fruticultura, Acuacultura y del Maguey de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0555-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0556-2026</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+      <c r="J557" t="inlineStr"/>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0556-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O557"/>
+  <dimension ref="A1:O562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24986,7 +24986,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="L519" t="inlineStr"/>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="M519" t="inlineStr">
         <is>
           <t>Estudios e Investigaciones (PIMUS de Huejutla de Reyes, PIMUS de Ixmiquilpan)</t>
@@ -25051,7 +25055,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr"/>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="M520" t="inlineStr">
         <is>
           <t>Equipo educativo para el Laboratorio de Innovación Agrícola Sustentable</t>
@@ -25181,7 +25189,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="L522" t="inlineStr"/>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="M522" t="inlineStr">
         <is>
           <t>Mantenimiento de Mobiliario y Equipo de Administración, Educacional y Recreativo, Impresiones y Publicaciones Oficiales</t>
@@ -25306,7 +25318,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr"/>
       <c r="M524" t="inlineStr">
         <is>
@@ -25367,7 +25383,11 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr"/>
       <c r="M525" t="inlineStr">
         <is>
@@ -25428,7 +25448,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr"/>
       <c r="M526" t="inlineStr">
         <is>
@@ -25486,7 +25510,7 @@
       <c r="I527" t="inlineStr"/>
       <c r="J527" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="K527" t="inlineStr"/>
@@ -25550,7 +25574,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr"/>
       <c r="M528" t="inlineStr">
         <is>
@@ -25611,7 +25639,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr"/>
       <c r="M529" t="inlineStr">
         <is>
@@ -26460,7 +26492,11 @@
       </c>
       <c r="H543" t="inlineStr"/>
       <c r="I543" t="inlineStr"/>
-      <c r="J543" t="inlineStr"/>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K543" t="inlineStr"/>
       <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr">
@@ -26517,7 +26553,11 @@
       </c>
       <c r="H544" t="inlineStr"/>
       <c r="I544" t="inlineStr"/>
-      <c r="J544" t="inlineStr"/>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K544" t="inlineStr"/>
       <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr">
@@ -26574,7 +26614,11 @@
       </c>
       <c r="H545" t="inlineStr"/>
       <c r="I545" t="inlineStr"/>
-      <c r="J545" t="inlineStr"/>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K545" t="inlineStr"/>
       <c r="L545" t="inlineStr"/>
       <c r="M545" t="inlineStr">
@@ -26631,7 +26675,11 @@
       </c>
       <c r="H546" t="inlineStr"/>
       <c r="I546" t="inlineStr"/>
-      <c r="J546" t="inlineStr"/>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K546" t="inlineStr"/>
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr">
@@ -26688,7 +26736,11 @@
       </c>
       <c r="H547" t="inlineStr"/>
       <c r="I547" t="inlineStr"/>
-      <c r="J547" t="inlineStr"/>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="K547" t="inlineStr"/>
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr">
@@ -27277,6 +27329,291 @@
         </is>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0557-2026</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+      <c r="J558" t="inlineStr"/>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Equipo de café) (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>la Subsecretaria de Desarrollo Agropecuario de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0557-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0558-2026</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr"/>
+      <c r="J559" t="inlineStr"/>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Bienes Informáticos, Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0558-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0559-2026</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr"/>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>Conservación y Mantenimiento Menor de Inmuebles</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>la Dirección General de Servicios Generales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0559-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0560-2026</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+      <c r="J561" t="inlineStr"/>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Equipamiento Especializado para el Laboratorio de Turismo</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0560-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0561-2026</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+      <c r="J562" t="inlineStr"/>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>Equipamiento Especializado para el Laboratorio de Ciencias</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0561-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O562"/>
+  <dimension ref="A1:O568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24522,7 +24522,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr"/>
       <c r="M512" t="inlineStr">
         <is>
@@ -24721,7 +24725,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr"/>
       <c r="M515" t="inlineStr">
         <is>
@@ -25323,7 +25331,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L524" t="inlineStr"/>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="M524" t="inlineStr">
         <is>
           <t>Equipamiento de la Orquesta Sinfónica del Estado de Hidalgo</t>
@@ -25453,7 +25465,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L526" t="inlineStr"/>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="M526" t="inlineStr">
         <is>
           <t>Plaguicidas, Abonos y Fertilizantes</t>
@@ -25579,7 +25595,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr"/>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="M528" t="inlineStr">
         <is>
           <t>Alimentación de Animales</t>
@@ -25644,7 +25664,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr"/>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="M529" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Módulos de Invernadero)</t>
@@ -25704,7 +25728,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr"/>
       <c r="M530" t="inlineStr">
         <is>
@@ -25765,7 +25793,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr"/>
       <c r="M531" t="inlineStr">
         <is>
@@ -25826,7 +25858,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr"/>
       <c r="M532" t="inlineStr">
         <is>
@@ -25887,7 +25923,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr">
         <is>
@@ -25948,7 +25988,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr">
         <is>
@@ -26009,7 +26053,11 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr"/>
       <c r="M535" t="inlineStr">
         <is>
@@ -26797,7 +26845,11 @@
       </c>
       <c r="H548" t="inlineStr"/>
       <c r="I548" t="inlineStr"/>
-      <c r="J548" t="inlineStr"/>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K548" t="inlineStr"/>
       <c r="L548" t="inlineStr"/>
       <c r="M548" t="inlineStr">
@@ -26854,7 +26906,11 @@
       </c>
       <c r="H549" t="inlineStr"/>
       <c r="I549" t="inlineStr"/>
-      <c r="J549" t="inlineStr"/>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K549" t="inlineStr"/>
       <c r="L549" t="inlineStr"/>
       <c r="M549" t="inlineStr">
@@ -26911,7 +26967,11 @@
       </c>
       <c r="H550" t="inlineStr"/>
       <c r="I550" t="inlineStr"/>
-      <c r="J550" t="inlineStr"/>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K550" t="inlineStr"/>
       <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr">
@@ -26968,7 +27028,11 @@
       </c>
       <c r="H551" t="inlineStr"/>
       <c r="I551" t="inlineStr"/>
-      <c r="J551" t="inlineStr"/>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K551" t="inlineStr"/>
       <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr">
@@ -27025,7 +27089,11 @@
       </c>
       <c r="H552" t="inlineStr"/>
       <c r="I552" t="inlineStr"/>
-      <c r="J552" t="inlineStr"/>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="K552" t="inlineStr"/>
       <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr">
@@ -27614,6 +27682,348 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0562-2026</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+      <c r="J563" t="inlineStr"/>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0562-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0563-2026</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>Herramientas Menores</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0563-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0564-2026</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>la Oficialía Mayor de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0564-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0565-2026</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N566" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0565-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0566-2026</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>Difusión de Programas y Actividades Gubernamentales</t>
+        </is>
+      </c>
+      <c r="N567" t="inlineStr">
+        <is>
+          <t>la Subsecretaría del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación e Inteligencia C5i de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0566-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0567-2026</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+      <c r="J568" t="inlineStr"/>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>Otros Arrendamientos (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N568" t="inlineStr">
+        <is>
+          <t>la Dirección General de Fomento Artesanal de la Secretaría de Bienestar e Inclusión Social, del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0567-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O568"/>
+  <dimension ref="A1:O572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24527,7 +24527,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L512" t="inlineStr"/>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M512" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -24730,7 +24734,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr"/>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M515" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -25733,7 +25741,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L530" t="inlineStr"/>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M530" t="inlineStr">
         <is>
           <t>Equipamiento para la asignación de espacios</t>
@@ -25863,7 +25875,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr"/>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M532" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -25928,7 +25944,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr"/>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M533" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Bienes Informáticos, Material Eléctrico</t>
@@ -25993,7 +26013,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr"/>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M534" t="inlineStr">
         <is>
           <t>Computadora de Escritorio</t>
@@ -26058,7 +26082,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr"/>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="M535" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros de Laboratorio</t>
@@ -26118,7 +26146,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr"/>
       <c r="M536" t="inlineStr">
         <is>
@@ -26179,7 +26211,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr"/>
       <c r="M537" t="inlineStr">
         <is>
@@ -26240,7 +26276,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr"/>
       <c r="M538" t="inlineStr">
         <is>
@@ -26301,7 +26341,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr">
         <is>
@@ -26359,7 +26403,7 @@
       <c r="I540" t="inlineStr"/>
       <c r="J540" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="K540" t="inlineStr"/>
@@ -26423,7 +26467,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr"/>
       <c r="M541" t="inlineStr">
         <is>
@@ -26484,7 +26532,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr"/>
       <c r="M542" t="inlineStr">
         <is>
@@ -27150,7 +27202,11 @@
       </c>
       <c r="H553" t="inlineStr"/>
       <c r="I553" t="inlineStr"/>
-      <c r="J553" t="inlineStr"/>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K553" t="inlineStr"/>
       <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr">
@@ -27207,7 +27263,11 @@
       </c>
       <c r="H554" t="inlineStr"/>
       <c r="I554" t="inlineStr"/>
-      <c r="J554" t="inlineStr"/>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K554" t="inlineStr"/>
       <c r="L554" t="inlineStr"/>
       <c r="M554" t="inlineStr">
@@ -27264,7 +27324,11 @@
       </c>
       <c r="H555" t="inlineStr"/>
       <c r="I555" t="inlineStr"/>
-      <c r="J555" t="inlineStr"/>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K555" t="inlineStr"/>
       <c r="L555" t="inlineStr"/>
       <c r="M555" t="inlineStr">
@@ -27321,7 +27385,11 @@
       </c>
       <c r="H556" t="inlineStr"/>
       <c r="I556" t="inlineStr"/>
-      <c r="J556" t="inlineStr"/>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K556" t="inlineStr"/>
       <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
@@ -27378,7 +27446,11 @@
       </c>
       <c r="H557" t="inlineStr"/>
       <c r="I557" t="inlineStr"/>
-      <c r="J557" t="inlineStr"/>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K557" t="inlineStr"/>
       <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
@@ -27549,7 +27621,11 @@
       </c>
       <c r="H560" t="inlineStr"/>
       <c r="I560" t="inlineStr"/>
-      <c r="J560" t="inlineStr"/>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="K560" t="inlineStr"/>
       <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr">
@@ -28024,6 +28100,234 @@
         </is>
       </c>
     </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0568-2026</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Materiales para el Mantenimiento de Señalizaciones (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N569" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0568-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0569-2026</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+      <c r="J570" t="inlineStr"/>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>Material Didáctico</t>
+        </is>
+      </c>
+      <c r="N570" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0569-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0570-2026</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+      <c r="J571" t="inlineStr"/>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Servicio Global para la Segunda Jornada Juvenil Cultural y Académica COBAEH 2026</t>
+        </is>
+      </c>
+      <c r="N571" t="inlineStr">
+        <is>
+          <t>el Colegio de Bachilleres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0570-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0571-2026</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+      <c r="J572" t="inlineStr"/>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N572" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0571-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
